--- a/docs/testing/PROJECT TEST CASES CAA 181026.xlsx
+++ b/docs/testing/PROJECT TEST CASES CAA 181026.xlsx
@@ -3150,7 +3150,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>E02-S05 - Scenario 1 (Previous event copied; T-98)</t>
+          <t>E02-S05 - Scenario 1 (Previous event copied; T-99)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>E09-S02 - Scenario 5 (Waiting list remains event-level; T-97)</t>
+          <t>E09-S02 - Scenario 5 (Waiting list remains event-level; T-98)</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>E09-S02 - Scenario 2 (Over-capacity submission remains Pending); T-97</t>
+          <t>E09-S02 - Scenario 2 (Over-capacity submission remains Pending); T-98</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>The request is saved as Pending for Organiser review; it does not consume an approved seat or create a Session waitlist (T-97)</t>
+          <t>The request is saved as Pending for Organiser review; it does not consume an approved seat or create a Session waitlist (T-98)</t>
         </is>
       </c>
     </row>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>E09-S04 - Scenario 1 (Joined a full Event's list); T-97</t>
+          <t>E09-S04 - Scenario 1 (Joined a full Event's list); T-98</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -16156,7 +16156,7 @@
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>attendee_i@example.com is added to the Event-level waiting list and receives confirmation; no Session-specific waiting-list entry is created (T-97)</t>
+          <t>attendee_i@example.com is added to the Event-level waiting list and receives confirmation; no Session-specific waiting-list entry is created (T-98)</t>
         </is>
       </c>
     </row>
